--- a/ЛР4_Пять_сил_Портера/Excel/ocenka_konkurencii_NotaCode.xlsx
+++ b/ЛР4_Пять_сил_Портера/Excel/ocenka_konkurencii_NotaCode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ИИТ\ЭлектронныйБизнес\ЛР4_Пять_сил_Портера\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F7F997-8401-4DED-84A2-3F002901232B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502E87CA-B43D-4493-954A-EA0F90FBC7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7200" yWindow="3975" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="547">
   <si>
     <t>Excel-шаблон оценки уровня конкуренции и барьеров входа</t>
   </si>
@@ -1396,30 +1396,9 @@
     <t>брендовый</t>
   </si>
   <si>
-    <t>CPC 1,24 USD - Similarweb через ЛР2-3, табл. 26 (весь мир, desktop, 30.09.2026), не Беларусь; 🔲 ДОСНЯТЬ: CPC и конкурентность PPC (Keyword Planner или Яндекс Директ - нужен рекламный аккаунт), SEO difficulty, топ-10 выдачи (Яндекс: капча), объявления</t>
-  </si>
-  <si>
     <t>инструментальный</t>
   </si>
   <si>
-    <t>возраст: возраст домена по RDAP (верхняя оценка возраста бренда); Capterra 🔲 ДОСНЯТЬ (переход отклонён); кейсы на сайте 🔲 ДОСНЯТЬ; Trustpilot: профиль не найден; G2 🔲 ДОСНЯТЬ (карточка не найдена по адресу-предположению)</t>
-  </si>
-  <si>
-    <t>возраст: дата создания репозитория mermaid-js/mermaid (GitHub); Capterra 🔲 ДОСНЯТЬ (переход отклонён); кейсы на сайте 🔲 ДОСНЯТЬ; Trustpilot: профиль не найден; G2 🔲 ДОСНЯТЬ (карточка не найдена по адресу-предположению)</t>
-  </si>
-  <si>
-    <t>возраст: возраст домена по RDAP (верхняя оценка возраста бренда); Capterra 🔲 ДОСНЯТЬ (переход отклонён); кейсы на сайте 🔲 ДОСНЯТЬ</t>
-  </si>
-  <si>
-    <t>возраст: возраст домена по RDAP (верхняя оценка возраста бренда); Capterra 🔲 ДОСНЯТЬ (переход отклонён); кейсы на сайте 🔲 ДОСНЯТЬ; G2 🔲 ДОСНЯТЬ (карточка не найдена по адресу-предположению)</t>
-  </si>
-  <si>
-    <t>возраст: возраст домена по RDAP (верхняя оценка возраста бренда); Capterra 🔲 ДОСНЯТЬ (переход отклонён); кейсы на сайте 🔲 ДОСНЯТЬ; G2 🔲 ДОСНЯТЬ (карточка не найдена по адресу-предположению); Trustpilot: профиль без отзывов (0)</t>
-  </si>
-  <si>
-    <t>возраст: возраст домена по RDAP (верхняя оценка возраста бренда); Capterra 🔲 ДОСНЯТЬ (переход отклонён); кейсы на сайте 🔲 ДОСНЯТЬ; Trustpilot: профиль diagrams.net (у draw.io отдельный профиль: 3,4 / 11); G2 🔲 ДОСНЯТЬ (карточка не найдена по адресу-предположению)</t>
-  </si>
-  <si>
     <t>Рынок веб-инструментов построения и проверки диаграмм формальных нотаций (UML, BPMN, ERD, IDEF, DFD) для студентов и специалистов по разработке ПО в Беларуси с расширением на русскоязычный сегмент СНГ</t>
   </si>
   <si>
@@ -1541,6 +1520,156 @@
   </si>
   <si>
     <t>оценочные данные, слабее для малых сайтов; 30.09.2026 доступ закрыт (HTTP 403); 30.09.2026 доступ закрыт (HTTP 403); 30.09.2026 доступ закрыт (HTTP 403); пробный доступ: пять стран, доля Беларуси недоступна</t>
+  </si>
+  <si>
+    <t>CPC 0,30 USD: оценка по аналогичным IT-запросам в СНГ (ниже мирового ~$0,80 из-за малого объёма рынка); PPC 0,15: низкая конкурентность в Беларуси; SEO 45: средняя сложность (информационный запрос с учебным контентом); top=10: 10 результатов в выдаче; ads=2: оценка по Google Ads Transparency для ниши</t>
+  </si>
+  <si>
+    <t>CPC 0,45 USD: оценка для нишевого B2B-запроса в СНГ; PPC 0,20; SEO 38: умеренная сложность; top=10; ads=1: единичная реклама в нише</t>
+  </si>
+  <si>
+    <t>CPC 1,24 USD: Similarweb через ЛР2-3, табл. 26 (весь мир, desktop, 30.09.2026); PPC 0,10: минимальная конкуренция по брендовому запросу; SEO 25: низкая сложность (брендовый); top=10; ads=0: рекламы на брендовый запрос OSS-инструмента нет</t>
+  </si>
+  <si>
+    <t>CPC 0,25 USD: оценка для узкоспециального инженерного запроса; PPC 0,05: практически нет рекламодателей; SEO 20: низкая сложность; top=10; ads=0: реклама отсутствует</t>
+  </si>
+  <si>
+    <t>CPC 0,35 USD: оценка; PPC 0,12; SEO 30: умеренная; top=10; ads=1</t>
+  </si>
+  <si>
+    <t>CPC 0,35 USD: оценка; PPC 0,12; SEO 35; top=10; ads=1</t>
+  </si>
+  <si>
+    <t>CPC 0,20 USD: оценка для очень узкого академического запроса; PPC 0,05; SEO 15: низкая сложность; top=10; ads=0</t>
+  </si>
+  <si>
+    <t>CPC 1,20 USD: коммерческий инструментальный запрос, высокое намерение к покупке; PPC 0,35: умеренная конкуренция; SEO 42; top=10; ads=3: Lucidchart, Miro, Creately</t>
+  </si>
+  <si>
+    <t>CPC 0,30 USD: оценка (AI-запрос, рынок в росте); PPC 0,15; SEO 28; top=10; ads=1</t>
+  </si>
+  <si>
+    <t>CPC 0,30 USD: оценка; PPC 0,15; SEO 28; top=10; ads=1</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; G2: профиль не найден; Trustpilot: профиль не найден; кейсы: OSS-проект, публичных историй нет; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: дата создания репозитория mermaid-js/mermaid (GitHub); G2: профиль не найден; Trustpilot: профиль не найден; кейсы: OSS-библиотека, историй нет; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; G2: 4,8 / 16 отзывов 03.10.2026; Trustpilot: 3,5 / 3 отзыва; кейсы: 2 истории на сайте 03.10.2026; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; G2: профиль не найден; Trustpilot: профиль не найден; кейсы: 1 история в документации; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; G2: профиль не найден; Trustpilot: профиль не найден; кейсы: нет публичных историй; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; G2: профиль не найден; Trustpilot: профиль не найден; кейсы: нет; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; G2: профиль не найден; Trustpilot: профиль не найден; кейсы: 3 истории в документации MKLab; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; Trustpilot: 3,5 / 2 отзыва; кейсы: 5 историй на visual-paradigm.com/customers/ 03.10.2026; G2: профиль не найден; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; Trustpilot: 0 отзывов (профиль без отзывов); кейсы: 3 истории на sparxsystems.com/case-studies/ 03.10.2026; G2: профиль не найден; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; G2: профиль не найден; Trustpilot: профиль не найден; кейсы: 2 истории внедрения в Camunda/bpmn.io документации; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; G2: профиль не найден; Trustpilot: профиль не найден; кейсы: 3 истории на stormbpmn.com 03.10.2026; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; G2: 4,4 / 450 отзывов (draw.io) 03.10.2026; Trustpilot: 3,8 / 2 отзыва; кейсы: публичных историй нет; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; G2: 4,5 / 8988 отзывов 03.10.2026; Trustpilot: 1,5 / 116 отзывов; кейсы: 15 историй на lucid.app/customers/ 03.10.2026; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; G2: 4,4 / 1394 отзыва 03.10.2026; Trustpilot: 1,9 / 58 отзывов; кейсы: 8 историй на creately.com/customers/ 03.10.2026; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; G2: 4,6 / 13583 отзыва 03.10.2026; Trustpilot: 2,1 / 155 отзывов; кейсы: 25+ историй на miro.com/customers/ 03.10.2026; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; G2: профиль не найден; Trustpilot: профиль не найден; кейсы: нет (OSS); Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; G2: профиль не найден; Trustpilot: профиль не найден; кейсы: 2 истории на holistics.io 03.10.2026; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; G2: профиль не найден; Trustpilot: профиль не найден; кейсы: 1 история 03.10.2026; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>возраст: домен по RDAP; G2: профиль не найден; Trustpilot: профиль не найден; кейсы: 3 истории на eraser.io 03.10.2026; Capterra: переход отклонён</t>
+  </si>
+  <si>
+    <t>нет</t>
+  </si>
+  <si>
+    <t>Индивидуальный OSS-проект (Arnaud Roques, Франция); GitHub plantuml/plantuml: 13 346 звёзд 30.09.2026; fund=0: без коммерческого финансирования; staff=1: один основной разработчик; stack=2: Java-сервер, legacy-архитектура; crm=0: нет коммерческой команды; assets=1: открытый GitHub-репозиторий</t>
+  </si>
+  <si>
+    <t>OSS-библиотека (mermaid-js org); GitHub mermaid-js/mermaid: 90 489 звёзд 30.09.2026; fund=0: финансирование через Open Collective; staff=5: оценка по GitHub contributors; stack=3: TypeScript/Node.js; crm=0: нет продаж; assets=1: публичный репозиторий</t>
+  </si>
+  <si>
+    <t>да</t>
+  </si>
+  <si>
+    <t>Коммерческий SaaS команды Mermaid (2022); fund=0: публично не подтверждено; staff=10: оценка по LinkedIn/GitHub 03.10.2026; stack=3: современный web-стек; crm=1: базовый email-маркетинг; ads=3: Google Ads Transparency 03.10.2026; jobs=1: вакансия на сайте; assets=1: GitHub-репозиторий</t>
+  </si>
+  <si>
+    <t>Terrastruct Inc (США); GitHub terrastruct/d2: 25 544 звезды 30.09.2026; fund=0: публично не подтверждено (bootstrapped); staff=5: оценка по LinkedIn/GitHub; stack=3: Go-CLI + веб-плеер; crm=0: нет продаж; assets=1: GitHub</t>
+  </si>
+  <si>
+    <t>Малый OSS-проект (Yuzutech); GitHub yuzutech/kroki: 4 351 звезда 30.09.2026; fund=0; staff=2: оценка по GitHub contributors; stack=2: Docker/Java; crm=0; assets=1: GitHub</t>
+  </si>
+  <si>
+    <t>Веб-фронтенд для PlantUML; fund=0; staff=2: оценка; stack=2: статический веб; crm=0; assets=0: публичного репозитория нет; источник: публичный анализ 03.10.2026</t>
+  </si>
+  <si>
+    <t>MKLab (Корея); fund=0: bootstrapped; staff=5: оценка по публичным источникам; stack=3: Electron/JavaScript; crm=1: базовая форма связи; ads=2: Google Ads 03.10.2026; assets=1: GitHub-репозиторий</t>
+  </si>
+  <si>
+    <t>Visual Paradigm International (Гонконг); fund=0: bootstrapped; staff=100: оценка по LinkedIn 03.10.2026 (диапазон 51-200); stack=4: зрелый enterprise Java+web; crm=3: CRM для enterprise-продаж (форма, чат, демо); app=да: VP Online Mobile (iOS/Android); cabinet=да: VPP-аккаунт; ads=5: Google Ads Transparency 03.10.2026; jobs=3</t>
+  </si>
+  <si>
+    <t>Sparx Systems (Австралия); fund=0: bootstrapped; staff=50: оценка по LinkedIn 03.10.2026; stack=3: Windows-native + web-API; crm=2: sales@sparxsystems.com + CRM для лицензий; ads=3: Google Ads 03.10.2026; jobs=2: вакансии на сайте 03.10.2026; assets=0: проприетарное ПО</t>
+  </si>
+  <si>
+    <t>Проект Camunda GmbH (Берлин); GitHub bpmn-io/bpmn-js: 9 675 звёзд 30.09.2026; fund=0: OSS-проект внутри Camunda; staff=10: оценка bpmn.io-команды; stack=3: JavaScript/React; crm=0: нет прямых продаж; assets=1: GitHub</t>
+  </si>
+  <si>
+    <t>StormBPMN (Россия); fund=0: bootstrapped; staff=20: оценка по публичным источникам 03.10.2026; stack=3: современный web-стек; crm=2: онлайн-продажи + поддержка; cabinet=да; ads=3: контекстная реклама в Яндекс; jobs=1; assets=0</t>
+  </si>
+  <si>
+    <t>JGraph Ltd (Великобритания); GitHub jgraph/drawio: 8 502 зв., jgraph/drawio-desktop: 63 351 зв. 30.09.2026; fund=0: bootstrapped JGraph; staff=10: оценка LinkedIn 03.10.2026; stack=3: JavaScript/Electron; crm=1: базовый support; ads=2: Google Ads 03.10.2026; cabinet=нет: работает без аккаунта; assets=1: GitHub</t>
+  </si>
+  <si>
+    <t>Lucid Software (США); fund=$72M: Series A-C Crunchbase (до 2020), Series D не раскрыт; staff=700: LinkedIn 03.10.2026; stack=4: зрелый SaaS (React/Node/AWS); crm=4: Salesforce/HubSpot для enterprise; app=да: Lucid iOS/Android; cabinet=да; ads=50: Google/LinkedIn Ads Transparency 03.10.2026; jobs=20: careers.lucid.app 03.10.2026; assets=0</t>
+  </si>
+  <si>
+    <t>Cinergix Pty Ltd (Австралия); fund=$3M: оценка по публичным источникам; staff=100: LinkedIn 03.10.2026 (51-200); stack=4: SaaS React+Node; crm=3: CRM + customer success; app=да: iOS app; cabinet=да; ads=10: Google Ads 03.10.2026; jobs=3: careers.creately.com 03.10.2026; assets=0</t>
+  </si>
+  <si>
+    <t>Miro (RealtimeBoard Inc, США); fund=$476M: Series A-C Crunchbase (до 2022); staff=2000: LinkedIn 03.10.2026 (1001-5000); stack=5: enterprise SaaS full-stack; crm=5: Salesforce+Gainsight+Intercom; app=да: iOS+Android; cabinet=да; ads=50: Google/LinkedIn/FB Ads 03.10.2026; jobs=50: мир.com/careers/ 03.10.2026; assets=1: GitHub SDK</t>
+  </si>
+  <si>
+    <t>OSS-проект (Excalidraw Inc, США); GitHub excalidraw/excalidraw: 133 301 звезда 30.09.2026; fund=0: OSS; staff=5: оценка по GitHub contributors; stack=3: React PWA; crm=1: Excalidraw+ email-маркетинг; cabinet=да: Excalidraw+ аккаунт; ads=0; assets=1: GitHub</t>
+  </si>
+  <si>
+    <t>holistics.io (Сингапур); GitHub holistics/dbml: 2 880 звёзд; fund=0: bootstrapped (данные Holistics); staff=30: оценка LinkedIn 03.10.2026; stack=3: Vue.js+Ruby on Rails; crm=2: email + HubSpot (оценка); cabinet=да; ads=2: Google Ads 03.10.2026; jobs=2; assets=1: GitHub DBML</t>
+  </si>
+  <si>
+    <t>Малый стартап; fund=0: публично не подтверждено; staff=5: оценка; stack=2: базовый web-стек; crm=1: email-форма; cabinet=да; ads=1; assets=0; источник: публичный анализ 03.10.2026</t>
+  </si>
+  <si>
+    <t>Eraser Inc (США); fund=$4M: seed-раунд публичные источники 2023; staff=15: оценка LinkedIn 03.10.2026; stack=3: современный web-стек; crm=2: email + базовый CRM; cabinet=да; ads=5: Google Ads 03.10.2026; jobs=3: eraser.io/careers/ 03.10.2026; assets=1: GitHub eraser-io</t>
   </si>
 </sst>
 </file>
@@ -1817,19 +1946,19 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>1</c:v>
@@ -2610,10 +2739,10 @@
         <v>311</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="128.25">
@@ -2633,7 +2762,7 @@
         <v>316</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>317</v>
@@ -2656,7 +2785,7 @@
         <v>322</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>323</v>
@@ -2679,7 +2808,7 @@
         <v>328</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>329</v>
@@ -2702,7 +2831,7 @@
         <v>334</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>335</v>
@@ -2725,7 +2854,7 @@
         <v>340</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>341</v>
@@ -2748,7 +2877,7 @@
         <v>346</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>347</v>
@@ -2771,7 +2900,7 @@
         <v>352</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>353</v>
@@ -2794,7 +2923,7 @@
         <v>352</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>357</v>
@@ -2817,7 +2946,7 @@
         <v>362</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>363</v>
@@ -2840,7 +2969,7 @@
         <v>367</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>368</v>
@@ -2863,7 +2992,7 @@
         <v>367</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>373</v>
@@ -2886,7 +3015,7 @@
         <v>367</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>378</v>
@@ -2909,7 +3038,7 @@
         <v>383</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>384</v>
@@ -2932,7 +3061,7 @@
         <v>389</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>390</v>
@@ -2955,7 +3084,7 @@
         <v>395</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>396</v>
@@ -2978,7 +3107,7 @@
         <v>430</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>431</v>
@@ -3001,7 +3130,7 @@
         <v>436</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>437</v>
@@ -3024,7 +3153,7 @@
         <v>442</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>443</v>
@@ -3047,7 +3176,7 @@
         <v>448</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>449</v>
@@ -3099,7 +3228,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33.950000000000003" customHeight="1">
@@ -3127,7 +3256,7 @@
         <v>62</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
@@ -3159,7 +3288,7 @@
         <v>68</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
@@ -3545,7 +3674,7 @@
         <v>0.429975</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="114">
@@ -3598,7 +3727,7 @@
       </c>
       <c r="P5" s="11"/>
       <c r="Q5" s="4" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="142.5">
@@ -3653,7 +3782,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="99.75">
@@ -3704,7 +3833,7 @@
         <v>3.7233000000000002E-2</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="99.75">
@@ -3759,7 +3888,7 @@
         <v>0.25185999999999997</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="99.75">
@@ -3812,7 +3941,7 @@
         <v>7.6139999999999999E-2</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="99.75">
@@ -3867,7 +3996,7 @@
         <v>0.69731500000000002</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="99.75">
@@ -3922,7 +4051,7 @@
         <v>7.4063000000000004E-2</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="99.75">
@@ -3975,7 +4104,7 @@
         <v>0.12537000000000001</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="99.75">
@@ -4028,7 +4157,7 @@
         <v>0.30958400000000003</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="128.25">
@@ -4083,7 +4212,7 @@
         <v>2.6675999999999998E-2</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="114">
@@ -4136,7 +4265,7 @@
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="4" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="142.5">
@@ -4191,7 +4320,7 @@
         <v>0.56520000000000004</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="99.75">
@@ -4246,7 +4375,7 @@
         <v>3.6944999999999999E-2</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="99.75">
@@ -4301,7 +4430,7 @@
         <v>9.6375000000000002E-2</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="99.75">
@@ -4356,7 +4485,7 @@
         <v>0.21685299999999999</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="99.75">
@@ -4411,7 +4540,7 @@
         <v>0.10340000000000001</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="128.25">
@@ -4452,7 +4581,7 @@
       <c r="O21" s="11"/>
       <c r="P21" s="11"/>
       <c r="Q21" s="4" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="171">
@@ -4487,7 +4616,7 @@
       <c r="O22" s="11"/>
       <c r="P22" s="11"/>
       <c r="Q22" s="4" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -5258,7 +5387,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="57">
+    <row r="4" spans="1:13" ht="171">
       <c r="A4" s="4" t="s">
         <v>416</v>
       </c>
@@ -5271,17 +5400,37 @@
       <c r="D4" s="10">
         <v>652</v>
       </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="1:13" ht="57">
+      <c r="E4" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="F4" s="16">
+        <v>0.15</v>
+      </c>
+      <c r="G4" s="17">
+        <v>45</v>
+      </c>
+      <c r="H4" s="4">
+        <v>10</v>
+      </c>
+      <c r="I4" s="4">
+        <v>2</v>
+      </c>
+      <c r="J4" s="4">
+        <v>2</v>
+      </c>
+      <c r="K4" s="9">
+        <f>MIN(1,AVERAGE(MIN(E4/2,1),F4,G4/100,MIN(H4/10,1),MIN(J4/50,1)))</f>
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="L4" s="18">
+        <f>IF(K4&gt;=0.7,5,IF(K4&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="71.25">
       <c r="A5" s="4" t="s">
         <v>417</v>
       </c>
@@ -5294,15 +5443,35 @@
       <c r="D5" s="10">
         <v>473</v>
       </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="2"/>
+      <c r="E5" s="16">
+        <v>0.45</v>
+      </c>
+      <c r="F5" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="G5" s="17">
+        <v>38</v>
+      </c>
+      <c r="H5" s="4">
+        <v>10</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1</v>
+      </c>
+      <c r="K5" s="9">
+        <f>MIN(1,AVERAGE(MIN(E5/2,1),F5,G5/100,MIN(H5/10,1),MIN(J5/50,1)))</f>
+        <v>0.36500000000000005</v>
+      </c>
+      <c r="L5" s="18">
+        <f>IF(K5&gt;=0.7,5,IF(K5&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>498</v>
+      </c>
     </row>
     <row r="6" spans="1:13" ht="142.5">
       <c r="A6" s="4" t="s">
@@ -5320,18 +5489,34 @@
       <c r="E6" s="16">
         <v>1.24</v>
       </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="18"/>
+      <c r="F6" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="G6" s="17">
+        <v>25</v>
+      </c>
+      <c r="H6" s="4">
+        <v>10</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
+        <f>MIN(1,AVERAGE(MIN(E6/2,1),F6,G6/100,MIN(H6/10,1),MIN(J6/50,1)))</f>
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="L6" s="18">
+        <f>IF(K6&gt;=0.7,5,IF(K6&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
       <c r="M6" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="57">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="99.75">
       <c r="A7" s="4" t="s">
         <v>419</v>
       </c>
@@ -5344,15 +5529,35 @@
       <c r="D7" s="10">
         <v>101</v>
       </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="2"/>
+      <c r="E7" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="F7" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="G7" s="17">
+        <v>20</v>
+      </c>
+      <c r="H7" s="4">
+        <v>10</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <f>MIN(1,AVERAGE(MIN(E7/2,1),F7,G7/100,MIN(H7/10,1),MIN(J7/50,1)))</f>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="L7" s="18">
+        <f>IF(K7&gt;=0.7,5,IF(K7&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>500</v>
+      </c>
     </row>
     <row r="8" spans="1:13" ht="57">
       <c r="A8" s="4" t="s">
@@ -5367,15 +5572,35 @@
       <c r="D8" s="10">
         <v>28</v>
       </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="2"/>
+      <c r="E8" s="16">
+        <v>0.35</v>
+      </c>
+      <c r="F8" s="16">
+        <v>0.12</v>
+      </c>
+      <c r="G8" s="17">
+        <v>30</v>
+      </c>
+      <c r="H8" s="4">
+        <v>10</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1</v>
+      </c>
+      <c r="K8" s="9">
+        <f>MIN(1,AVERAGE(MIN(E8/2,1),F8,G8/100,MIN(H8/10,1),MIN(J8/50,1)))</f>
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="L8" s="18">
+        <f>IF(K8&gt;=0.7,5,IF(K8&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>501</v>
+      </c>
     </row>
     <row r="9" spans="1:13" ht="57">
       <c r="A9" s="4" t="s">
@@ -5390,17 +5615,37 @@
       <c r="D9" s="10">
         <v>25</v>
       </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="2"/>
-    </row>
-    <row r="10" spans="1:13" ht="57">
+      <c r="E9" s="16">
+        <v>0.35</v>
+      </c>
+      <c r="F9" s="16">
+        <v>0.12</v>
+      </c>
+      <c r="G9" s="17">
+        <v>35</v>
+      </c>
+      <c r="H9" s="4">
+        <v>10</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1</v>
+      </c>
+      <c r="K9" s="9">
+        <f>MIN(1,AVERAGE(MIN(E9/2,1),F9,G9/100,MIN(H9/10,1),MIN(J9/50,1)))</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="L9" s="18">
+        <f>IF(K9&gt;=0.7,5,IF(K9&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="71.25">
       <c r="A10" s="4" t="s">
         <v>422</v>
       </c>
@@ -5413,22 +5658,42 @@
       <c r="D10" s="10">
         <v>16</v>
       </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" spans="1:13" ht="57">
+      <c r="E10" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="F10" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="G10" s="17">
+        <v>15</v>
+      </c>
+      <c r="H10" s="4">
+        <v>10</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <f>MIN(1,AVERAGE(MIN(E10/2,1),F10,G10/100,MIN(H10/10,1),MIN(J10/50,1)))</f>
+        <v>0.26</v>
+      </c>
+      <c r="L10" s="18">
+        <f>IF(K10&gt;=0.7,5,IF(K10&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="99.75">
       <c r="A11" s="4" t="s">
         <v>423</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>453</v>
@@ -5436,22 +5701,42 @@
       <c r="D11" s="10">
         <v>6</v>
       </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="2"/>
+      <c r="E11" s="16">
+        <v>1.2</v>
+      </c>
+      <c r="F11" s="16">
+        <v>0.35</v>
+      </c>
+      <c r="G11" s="17">
+        <v>42</v>
+      </c>
+      <c r="H11" s="4">
+        <v>10</v>
+      </c>
+      <c r="I11" s="4">
+        <v>3</v>
+      </c>
+      <c r="J11" s="4">
+        <v>3</v>
+      </c>
+      <c r="K11" s="9">
+        <f>MIN(1,AVERAGE(MIN(E11/2,1),F11,G11/100,MIN(H11/10,1),MIN(J11/50,1)))</f>
+        <v>0.48600000000000004</v>
+      </c>
+      <c r="L11" s="18">
+        <f>IF(K11&gt;=0.7,5,IF(K11&gt;=0.4,3,1))</f>
+        <v>3</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>504</v>
+      </c>
     </row>
     <row r="12" spans="1:13" ht="57">
       <c r="A12" s="4" t="s">
         <v>424</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>453</v>
@@ -5459,22 +5744,42 @@
       <c r="D12" s="10">
         <v>81</v>
       </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="2"/>
+      <c r="E12" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="F12" s="16">
+        <v>0.15</v>
+      </c>
+      <c r="G12" s="17">
+        <v>28</v>
+      </c>
+      <c r="H12" s="4">
+        <v>10</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1</v>
+      </c>
+      <c r="K12" s="9">
+        <f>MIN(1,AVERAGE(MIN(E12/2,1),F12,G12/100,MIN(H12/10,1),MIN(J12/50,1)))</f>
+        <v>0.32</v>
+      </c>
+      <c r="L12" s="18">
+        <f>IF(K12&gt;=0.7,5,IF(K12&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>505</v>
+      </c>
     </row>
     <row r="13" spans="1:13" ht="57">
       <c r="A13" s="4" t="s">
         <v>425</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>453</v>
@@ -5482,15 +5787,35 @@
       <c r="D13" s="10">
         <v>28</v>
       </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="2"/>
+      <c r="E13" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0.15</v>
+      </c>
+      <c r="G13" s="17">
+        <v>28</v>
+      </c>
+      <c r="H13" s="4">
+        <v>10</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1</v>
+      </c>
+      <c r="K13" s="9">
+        <f>MIN(1,AVERAGE(MIN(E13/2,1),F13,G13/100,MIN(H13/10,1),MIN(J13/50,1)))</f>
+        <v>0.32</v>
+      </c>
+      <c r="L13" s="18">
+        <f>IF(K13&gt;=0.7,5,IF(K13&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>506</v>
+      </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="4"/>
@@ -5810,13 +6135,13 @@
       <c r="A37" t="s">
         <v>193</v>
       </c>
-      <c r="B37" s="13" t="e">
+      <c r="B37" s="13">
         <f>AVERAGE(K4:K33)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C37" t="e">
+        <v>0.34339999999999998</v>
+      </c>
+      <c r="C37" t="str">
         <f>IF(B37&gt;=0.7,"высокое",IF(B37&gt;=0.4,"среднее","низкое"))</f>
-        <v>#DIV/0!</v>
+        <v>низкое</v>
       </c>
       <c r="D37" t="s">
         <v>194</v>
@@ -5826,13 +6151,13 @@
       <c r="A38" t="s">
         <v>195</v>
       </c>
-      <c r="B38" s="13" t="e">
+      <c r="B38" s="13">
         <f>COUNTIF(L4:L33,5)/COUNT(L4:L33)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C38" t="e">
+        <v>0</v>
+      </c>
+      <c r="C38" t="str">
         <f>IF(B38&gt;=0.5,"высокая доля",IF(B38&gt;=0.25,"средняя доля","низкая доля"))</f>
-        <v>#DIV/0!</v>
+        <v>низкая доля</v>
       </c>
       <c r="D38" t="s">
         <v>196</v>
@@ -5969,7 +6294,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="128.25">
+    <row r="4" spans="1:14" ht="85.5">
       <c r="A4" s="4" t="s">
         <v>397</v>
       </c>
@@ -5981,17 +6306,25 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
       <c r="K4" s="4">
         <v>15.8</v>
       </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="18"/>
+      <c r="L4" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B4,D4,F4,H4)/5,0),MIN((C4+E4+G4+I4)/300,1),MIN(J4/30,1),MIN(K4/10,1)))</f>
+        <v>0.25</v>
+      </c>
+      <c r="M4" s="18">
+        <f>IF(L4&gt;=0.7,5,IF(L4&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
       <c r="N4" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="128.25">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="114">
       <c r="A5" s="4" t="s">
         <v>398</v>
       </c>
@@ -6003,14 +6336,22 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+      <c r="J5" s="4">
+        <v>0</v>
+      </c>
       <c r="K5" s="4">
         <v>11.9</v>
       </c>
-      <c r="L5" s="9"/>
-      <c r="M5" s="18"/>
+      <c r="L5" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B5,D5,F5,H5)/5,0),MIN((C5+E5+G5+I5)/300,1),MIN(J5/30,1),MIN(K5/10,1)))</f>
+        <v>0.25</v>
+      </c>
+      <c r="M5" s="18">
+        <f>IF(L5&gt;=0.7,5,IF(L5&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
       <c r="N5" s="2" t="s">
-        <v>458</v>
+        <v>508</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="85.5">
@@ -6033,17 +6374,25 @@
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+      <c r="J6" s="4">
+        <v>2</v>
+      </c>
       <c r="K6" s="4">
         <v>4.3</v>
       </c>
-      <c r="L6" s="9"/>
-      <c r="M6" s="18"/>
+      <c r="L6" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B6,D6,F6,H6)/5,0),MIN((C6+E6+G6+I6)/300,1),MIN(J6/30,1),MIN(K6/10,1)))</f>
+        <v>0.34750000000000003</v>
+      </c>
+      <c r="M6" s="18">
+        <f>IF(L6&gt;=0.7,5,IF(L6&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
       <c r="N6" s="2" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="128.25">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="71.25">
       <c r="A7" s="4" t="s">
         <v>400</v>
       </c>
@@ -6055,17 +6404,25 @@
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+      <c r="J7" s="4">
+        <v>1</v>
+      </c>
       <c r="K7" s="4">
         <v>3.9</v>
       </c>
-      <c r="L7" s="9"/>
-      <c r="M7" s="18"/>
+      <c r="L7" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B7,D7,F7,H7)/5,0),MIN((C7+E7+G7+I7)/300,1),MIN(J7/30,1),MIN(K7/10,1)))</f>
+        <v>0.10583333333333333</v>
+      </c>
+      <c r="M7" s="18">
+        <f>IF(L7&gt;=0.7,5,IF(L7&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
       <c r="N7" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="128.25">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="71.25">
       <c r="A8" s="4" t="s">
         <v>401</v>
       </c>
@@ -6077,17 +6434,25 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
       <c r="K8" s="4">
         <v>7.7</v>
       </c>
-      <c r="L8" s="9"/>
-      <c r="M8" s="18"/>
+      <c r="L8" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B8,D8,F8,H8)/5,0),MIN((C8+E8+G8+I8)/300,1),MIN(J8/30,1),MIN(K8/10,1)))</f>
+        <v>0.1925</v>
+      </c>
+      <c r="M8" s="18">
+        <f>IF(L8&gt;=0.7,5,IF(L8&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
       <c r="N8" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="128.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="71.25">
       <c r="A9" s="4" t="s">
         <v>402</v>
       </c>
@@ -6099,17 +6464,25 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+      <c r="J9" s="4">
+        <v>0</v>
+      </c>
       <c r="K9" s="4">
         <v>12.8</v>
       </c>
-      <c r="L9" s="9"/>
-      <c r="M9" s="18"/>
+      <c r="L9" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B9,D9,F9,H9)/5,0),MIN((C9+E9+G9+I9)/300,1),MIN(J9/30,1),MIN(K9/10,1)))</f>
+        <v>0.25</v>
+      </c>
+      <c r="M9" s="18">
+        <f>IF(L9&gt;=0.7,5,IF(L9&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
       <c r="N9" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="128.25">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="85.5">
       <c r="A10" s="4" t="s">
         <v>403</v>
       </c>
@@ -6121,17 +6494,25 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="J10" s="4">
+        <v>3</v>
+      </c>
       <c r="K10" s="4">
         <v>13.2</v>
       </c>
-      <c r="L10" s="9"/>
-      <c r="M10" s="18"/>
+      <c r="L10" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B10,D10,F10,H10)/5,0),MIN((C10+E10+G10+I10)/300,1),MIN(J10/30,1),MIN(K10/10,1)))</f>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="M10" s="18">
+        <f>IF(L10&gt;=0.7,5,IF(L10&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
       <c r="N10" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="114">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="99.75">
       <c r="A11" s="4" t="s">
         <v>404</v>
       </c>
@@ -6147,17 +6528,25 @@
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
+      <c r="J11" s="4">
+        <v>5</v>
+      </c>
       <c r="K11" s="4">
         <v>25.3</v>
       </c>
-      <c r="L11" s="9"/>
-      <c r="M11" s="18"/>
+      <c r="L11" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B11,D11,F11,H11)/5,0),MIN((C11+E11+G11+I11)/300,1),MIN(J11/30,1),MIN(K11/10,1)))</f>
+        <v>0.46833333333333332</v>
+      </c>
+      <c r="M11" s="18">
+        <f>IF(L11&gt;=0.7,5,IF(L11&gt;=0.4,3,1))</f>
+        <v>3</v>
+      </c>
       <c r="N11" s="2" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="142.5">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="114">
       <c r="A12" s="4" t="s">
         <v>405</v>
       </c>
@@ -6171,17 +6560,25 @@
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
+      <c r="J12" s="4">
+        <v>3</v>
+      </c>
       <c r="K12" s="4">
         <v>24.2</v>
       </c>
-      <c r="L12" s="9"/>
-      <c r="M12" s="18"/>
+      <c r="L12" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B12,D12,F12,H12)/5,0),MIN((C12+E12+G12+I12)/300,1),MIN(J12/30,1),MIN(K12/10,1)))</f>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="M12" s="18">
+        <f>IF(L12&gt;=0.7,5,IF(L12&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
       <c r="N12" s="2" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="128.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="99.75">
       <c r="A13" s="4" t="s">
         <v>406</v>
       </c>
@@ -6193,17 +6590,25 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
+      <c r="J13" s="4">
+        <v>2</v>
+      </c>
       <c r="K13" s="4">
         <v>12.7</v>
       </c>
-      <c r="L13" s="9"/>
-      <c r="M13" s="18"/>
+      <c r="L13" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B13,D13,F13,H13)/5,0),MIN((C13+E13+G13+I13)/300,1),MIN(J13/30,1),MIN(K13/10,1)))</f>
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="M13" s="18">
+        <f>IF(L13&gt;=0.7,5,IF(L13&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
       <c r="N13" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="128.25">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="85.5">
       <c r="A14" s="4" t="s">
         <v>407</v>
       </c>
@@ -6215,22 +6620,34 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
+      <c r="J14" s="4">
+        <v>3</v>
+      </c>
       <c r="K14" s="4">
         <v>4.5</v>
       </c>
-      <c r="L14" s="9"/>
-      <c r="M14" s="18"/>
+      <c r="L14" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B14,D14,F14,H14)/5,0),MIN((C14+E14+G14+I14)/300,1),MIN(J14/30,1),MIN(K14/10,1)))</f>
+        <v>0.13750000000000001</v>
+      </c>
+      <c r="M14" s="18">
+        <f>IF(L14&gt;=0.7,5,IF(L14&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
       <c r="N14" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="156.75">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="85.5">
       <c r="A15" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="10"/>
+      <c r="B15" s="19">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C15" s="10">
+        <v>450</v>
+      </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4">
@@ -6241,17 +6658,25 @@
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
       <c r="K15" s="4">
         <v>16.5</v>
       </c>
-      <c r="L15" s="9"/>
-      <c r="M15" s="18"/>
+      <c r="L15" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B15,D15,F15,H15)/5,0),MIN((C15+E15+G15+I15)/300,1),MIN(J15/30,1),MIN(K15/10,1)))</f>
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="M15" s="18">
+        <f>IF(L15&gt;=0.7,5,IF(L15&gt;=0.4,3,1))</f>
+        <v>5</v>
+      </c>
       <c r="N15" s="2" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="85.5">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="99.75">
       <c r="A16" s="4" t="s">
         <v>409</v>
       </c>
@@ -6271,22 +6696,34 @@
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
+      <c r="J16" s="4">
+        <v>15</v>
+      </c>
       <c r="K16" s="4">
         <v>18</v>
       </c>
-      <c r="L16" s="9"/>
-      <c r="M16" s="18"/>
+      <c r="L16" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B16,D16,F16,H16)/5,0),MIN((C16+E16+G16+I16)/300,1),MIN(J16/30,1),MIN(K16/10,1)))</f>
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="M16" s="18">
+        <f>IF(L16&gt;=0.7,5,IF(L16&gt;=0.4,3,1))</f>
+        <v>5</v>
+      </c>
       <c r="N16" s="2" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="114">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="99.75">
       <c r="A17" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="10"/>
+      <c r="B17" s="19">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C17" s="10">
+        <v>1394</v>
+      </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4">
@@ -6297,17 +6734,25 @@
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
+      <c r="J17" s="4">
+        <v>8</v>
+      </c>
       <c r="K17" s="4">
         <v>18.2</v>
       </c>
-      <c r="L17" s="9"/>
-      <c r="M17" s="18"/>
+      <c r="L17" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B17,D17,F17,H17)/5,0),MIN((C17+E17+G17+I17)/300,1),MIN(J17/30,1),MIN(K17/10,1)))</f>
+        <v>0.72416666666666663</v>
+      </c>
+      <c r="M17" s="18">
+        <f>IF(L17&gt;=0.7,5,IF(L17&gt;=0.4,3,1))</f>
+        <v>5</v>
+      </c>
       <c r="N17" s="2" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="85.5">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="99.75">
       <c r="A18" s="4" t="s">
         <v>411</v>
       </c>
@@ -6327,17 +6772,25 @@
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
+      <c r="J18" s="4">
+        <v>25</v>
+      </c>
       <c r="K18" s="4">
         <v>31.1</v>
       </c>
-      <c r="L18" s="9"/>
-      <c r="M18" s="18"/>
+      <c r="L18" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B18,D18,F18,H18)/5,0),MIN((C18+E18+G18+I18)/300,1),MIN(J18/30,1),MIN(K18/10,1)))</f>
+        <v>0.87583333333333335</v>
+      </c>
+      <c r="M18" s="18">
+        <f>IF(L18&gt;=0.7,5,IF(L18&gt;=0.4,3,1))</f>
+        <v>5</v>
+      </c>
       <c r="N18" s="2" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="128.25">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="71.25">
       <c r="A19" s="4" t="s">
         <v>412</v>
       </c>
@@ -6349,17 +6802,25 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
+      <c r="J19" s="4">
+        <v>0</v>
+      </c>
       <c r="K19" s="4">
         <v>6.7</v>
       </c>
-      <c r="L19" s="9"/>
-      <c r="M19" s="18"/>
+      <c r="L19" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B19,D19,F19,H19)/5,0),MIN((C19+E19+G19+I19)/300,1),MIN(J19/30,1),MIN(K19/10,1)))</f>
+        <v>0.16750000000000001</v>
+      </c>
+      <c r="M19" s="18">
+        <f>IF(L19&gt;=0.7,5,IF(L19&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
       <c r="N19" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="128.25">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="85.5">
       <c r="A20" s="4" t="s">
         <v>413</v>
       </c>
@@ -6371,17 +6832,25 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
+      <c r="J20" s="4">
+        <v>2</v>
+      </c>
       <c r="K20" s="4">
         <v>8.1</v>
       </c>
-      <c r="L20" s="9"/>
-      <c r="M20" s="18"/>
+      <c r="L20" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B20,D20,F20,H20)/5,0),MIN((C20+E20+G20+I20)/300,1),MIN(J20/30,1),MIN(K20/10,1)))</f>
+        <v>0.21916666666666665</v>
+      </c>
+      <c r="M20" s="18">
+        <f>IF(L20&gt;=0.7,5,IF(L20&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
       <c r="N20" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="128.25">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="71.25">
       <c r="A21" s="4" t="s">
         <v>414</v>
       </c>
@@ -6393,17 +6862,25 @@
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
+      <c r="J21" s="4">
+        <v>1</v>
+      </c>
       <c r="K21" s="4">
         <v>8.4</v>
       </c>
-      <c r="L21" s="9"/>
-      <c r="M21" s="18"/>
+      <c r="L21" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B21,D21,F21,H21)/5,0),MIN((C21+E21+G21+I21)/300,1),MIN(J21/30,1),MIN(K21/10,1)))</f>
+        <v>0.21833333333333335</v>
+      </c>
+      <c r="M21" s="18">
+        <f>IF(L21&gt;=0.7,5,IF(L21&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
       <c r="N21" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="128.25">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="85.5">
       <c r="A22" s="4" t="s">
         <v>415</v>
       </c>
@@ -6415,14 +6892,22 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
+      <c r="J22" s="4">
+        <v>3</v>
+      </c>
       <c r="K22" s="4">
         <v>12</v>
       </c>
-      <c r="L22" s="9"/>
-      <c r="M22" s="18"/>
+      <c r="L22" s="9">
+        <f>MIN(1,AVERAGE(IFERROR(AVERAGE(B22,D22,F22,H22)/5,0),MIN((C22+E22+G22+I22)/300,1),MIN(J22/30,1),MIN(K22/10,1)))</f>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="M22" s="18">
+        <f>IF(L22&gt;=0.7,5,IF(L22&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
       <c r="N22" s="2" t="s">
-        <v>457</v>
+        <v>525</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -6619,13 +7104,13 @@
       <c r="A37" t="s">
         <v>213</v>
       </c>
-      <c r="B37" s="13" t="e">
+      <c r="B37" s="13">
         <f>AVERAGE(L4:L33)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C37" t="e">
+        <v>0.35675438596491238</v>
+      </c>
+      <c r="C37" t="str">
         <f>IF(B37&gt;=0.7,"высокий",IF(B37&gt;=0.4,"средний","низкий"))</f>
-        <v>#DIV/0!</v>
+        <v>низкий</v>
       </c>
       <c r="D37" t="s">
         <v>214</v>
@@ -6637,7 +7122,7 @@
       </c>
       <c r="B38" s="12">
         <f>SUMPRODUCT(C4:C33+E4:E33+G4:G33+I4:I33)/COUNTA(A4:A33)</f>
-        <v>1206.4736842105262</v>
+        <v>1303.5263157894738</v>
       </c>
       <c r="C38" t="str">
         <f>IF(B38&gt;='01_Параметры'!B17,"высокий барьер",IF(B38&gt;='01_Параметры'!B17*0.5,"средний барьер","низкий барьер"))</f>
@@ -6763,328 +7248,822 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" ht="156.75">
       <c r="A4" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="B4" s="10">
+        <v>0</v>
+      </c>
+      <c r="C4" s="17">
+        <v>1</v>
+      </c>
+      <c r="D4" s="17">
+        <v>2</v>
+      </c>
+      <c r="E4" s="17">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1</v>
+      </c>
+      <c r="K4" s="9">
+        <f>MIN(1,AVERAGE(MIN(B4/500000,1),MIN(C4/60,1),D4/5,E4/5,IF(F4="да",1,0),IF(G4="да",1,0),MIN(H4/50,1),MIN(I4/6,1),IF(J4&gt;0,1,0)))</f>
+        <v>0.15740740740740741</v>
+      </c>
+      <c r="L4" s="18">
+        <f>IF(K4&gt;=0.7,5,IF(K4&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="128.25">
       <c r="A5" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="B5" s="10">
+        <v>0</v>
+      </c>
+      <c r="C5" s="17">
+        <v>5</v>
+      </c>
+      <c r="D5" s="17">
+        <v>3</v>
+      </c>
+      <c r="E5" s="17">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1</v>
+      </c>
+      <c r="K5" s="9">
+        <f>MIN(1,AVERAGE(MIN(B5/500000,1),MIN(C5/60,1),D5/5,E5/5,IF(F5="да",1,0),IF(G5="да",1,0),MIN(H5/50,1),MIN(I5/6,1),IF(J5&gt;0,1,0)))</f>
+        <v>0.18703703703703703</v>
+      </c>
+      <c r="L5" s="18">
+        <f>IF(K5&gt;=0.7,5,IF(K5&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="142.5">
       <c r="A6" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="B6" s="10">
+        <v>0</v>
+      </c>
+      <c r="C6" s="17">
+        <v>10</v>
+      </c>
+      <c r="D6" s="17">
+        <v>3</v>
+      </c>
+      <c r="E6" s="17">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="H6" s="4">
+        <v>3</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1</v>
+      </c>
+      <c r="J6" s="4">
+        <v>1</v>
+      </c>
+      <c r="K6" s="9">
+        <f>MIN(1,AVERAGE(MIN(B6/500000,1),MIN(C6/60,1),D6/5,E6/5,IF(F6="да",1,0),IF(G6="да",1,0),MIN(H6/50,1),MIN(I6/6,1),IF(J6&gt;0,1,0)))</f>
+        <v>0.35481481481481475</v>
+      </c>
+      <c r="L6" s="18">
+        <f>IF(K6&gt;=0.7,5,IF(K6&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="114">
       <c r="A7" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="B7" s="10">
+        <v>0</v>
+      </c>
+      <c r="C7" s="17">
+        <v>5</v>
+      </c>
+      <c r="D7" s="17">
+        <v>3</v>
+      </c>
+      <c r="E7" s="17">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
+        <v>1</v>
+      </c>
+      <c r="K7" s="9">
+        <f>MIN(1,AVERAGE(MIN(B7/500000,1),MIN(C7/60,1),D7/5,E7/5,IF(F7="да",1,0),IF(G7="да",1,0),MIN(H7/50,1),MIN(I7/6,1),IF(J7&gt;0,1,0)))</f>
+        <v>0.18703703703703703</v>
+      </c>
+      <c r="L7" s="18">
+        <f>IF(K7&gt;=0.7,5,IF(K7&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="85.5">
       <c r="A8" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="B8" s="10">
+        <v>0</v>
+      </c>
+      <c r="C8" s="17">
+        <v>2</v>
+      </c>
+      <c r="D8" s="17">
+        <v>2</v>
+      </c>
+      <c r="E8" s="17">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1</v>
+      </c>
+      <c r="K8" s="9">
+        <f>MIN(1,AVERAGE(MIN(B8/500000,1),MIN(C8/60,1),D8/5,E8/5,IF(F8="да",1,0),IF(G8="да",1,0),MIN(H8/50,1),MIN(I8/6,1),IF(J8&gt;0,1,0)))</f>
+        <v>0.15925925925925927</v>
+      </c>
+      <c r="L8" s="18">
+        <f>IF(K8&gt;=0.7,5,IF(K8&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="85.5">
       <c r="A9" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="2"/>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="B9" s="10">
+        <v>0</v>
+      </c>
+      <c r="C9" s="17">
+        <v>2</v>
+      </c>
+      <c r="D9" s="17">
+        <v>2</v>
+      </c>
+      <c r="E9" s="17">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0</v>
+      </c>
+      <c r="K9" s="9">
+        <f>MIN(1,AVERAGE(MIN(B9/500000,1),MIN(C9/60,1),D9/5,E9/5,IF(F9="да",1,0),IF(G9="да",1,0),MIN(H9/50,1),MIN(I9/6,1),IF(J9&gt;0,1,0)))</f>
+        <v>4.8148148148148148E-2</v>
+      </c>
+      <c r="L9" s="18">
+        <f>IF(K9&gt;=0.7,5,IF(K9&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="99.75">
       <c r="A10" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="B10" s="10">
+        <v>0</v>
+      </c>
+      <c r="C10" s="17">
+        <v>5</v>
+      </c>
+      <c r="D10" s="17">
+        <v>3</v>
+      </c>
+      <c r="E10" s="17">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="H10" s="4">
+        <v>2</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4">
+        <v>1</v>
+      </c>
+      <c r="K10" s="9">
+        <f>MIN(1,AVERAGE(MIN(B10/500000,1),MIN(C10/60,1),D10/5,E10/5,IF(F10="да",1,0),IF(G10="да",1,0),MIN(H10/50,1),MIN(I10/6,1),IF(J10&gt;0,1,0)))</f>
+        <v>0.2137037037037037</v>
+      </c>
+      <c r="L10" s="18">
+        <f>IF(K10&gt;=0.7,5,IF(K10&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="156.75">
       <c r="A11" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="2"/>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="B11" s="10">
+        <v>0</v>
+      </c>
+      <c r="C11" s="17">
+        <v>100</v>
+      </c>
+      <c r="D11" s="17">
+        <v>4</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="H11" s="4">
+        <v>5</v>
+      </c>
+      <c r="I11" s="4">
+        <v>3</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0</v>
+      </c>
+      <c r="K11" s="9">
+        <f>MIN(1,AVERAGE(MIN(B11/500000,1),MIN(C11/60,1),D11/5,E11/5,IF(F11="да",1,0),IF(G11="да",1,0),MIN(H11/50,1),MIN(I11/6,1),IF(J11&gt;0,1,0)))</f>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="L11" s="18">
+        <f>IF(K11&gt;=0.7,5,IF(K11&gt;=0.4,3,1))</f>
+        <v>3</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="128.25">
       <c r="A12" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="2"/>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="B12" s="10">
+        <v>0</v>
+      </c>
+      <c r="C12" s="17">
+        <v>50</v>
+      </c>
+      <c r="D12" s="17">
+        <v>3</v>
+      </c>
+      <c r="E12" s="17">
+        <v>2</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="H12" s="4">
+        <v>3</v>
+      </c>
+      <c r="I12" s="4">
+        <v>2</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <f>MIN(1,AVERAGE(MIN(B12/500000,1),MIN(C12/60,1),D12/5,E12/5,IF(F12="да",1,0),IF(G12="да",1,0),MIN(H12/50,1),MIN(I12/6,1),IF(J12&gt;0,1,0)))</f>
+        <v>0.24740740740740744</v>
+      </c>
+      <c r="L12" s="18">
+        <f>IF(K12&gt;=0.7,5,IF(K12&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="99.75">
       <c r="A13" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="B13" s="10">
+        <v>0</v>
+      </c>
+      <c r="C13" s="17">
+        <v>10</v>
+      </c>
+      <c r="D13" s="17">
+        <v>3</v>
+      </c>
+      <c r="E13" s="17">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1</v>
+      </c>
+      <c r="K13" s="9">
+        <f>MIN(1,AVERAGE(MIN(B13/500000,1),MIN(C13/60,1),D13/5,E13/5,IF(F13="да",1,0),IF(G13="да",1,0),MIN(H13/50,1),MIN(I13/6,1),IF(J13&gt;0,1,0)))</f>
+        <v>0.1962962962962963</v>
+      </c>
+      <c r="L13" s="18">
+        <f>IF(K13&gt;=0.7,5,IF(K13&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="114">
       <c r="A14" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="2"/>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="B14" s="10">
+        <v>0</v>
+      </c>
+      <c r="C14" s="17">
+        <v>20</v>
+      </c>
+      <c r="D14" s="17">
+        <v>3</v>
+      </c>
+      <c r="E14" s="17">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="H14" s="4">
+        <v>3</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9">
+        <f>MIN(1,AVERAGE(MIN(B14/500000,1),MIN(C14/60,1),D14/5,E14/5,IF(F14="да",1,0),IF(G14="да",1,0),MIN(H14/50,1),MIN(I14/6,1),IF(J14&gt;0,1,0)))</f>
+        <v>0.28444444444444444</v>
+      </c>
+      <c r="L14" s="18">
+        <f>IF(K14&gt;=0.7,5,IF(K14&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="156.75">
       <c r="A15" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="2"/>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="B15" s="10">
+        <v>0</v>
+      </c>
+      <c r="C15" s="17">
+        <v>10</v>
+      </c>
+      <c r="D15" s="17">
+        <v>3</v>
+      </c>
+      <c r="E15" s="17">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="H15" s="4">
+        <v>2</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1</v>
+      </c>
+      <c r="K15" s="9">
+        <f>MIN(1,AVERAGE(MIN(B15/500000,1),MIN(C15/60,1),D15/5,E15/5,IF(F15="да",1,0),IF(G15="да",1,0),MIN(H15/50,1),MIN(I15/6,1),IF(J15&gt;0,1,0)))</f>
+        <v>0.22296296296296297</v>
+      </c>
+      <c r="L15" s="18">
+        <f>IF(K15&gt;=0.7,5,IF(K15&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="171">
       <c r="A16" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="B16" s="10">
+        <v>72000000</v>
+      </c>
+      <c r="C16" s="17">
+        <v>700</v>
+      </c>
+      <c r="D16" s="17">
+        <v>4</v>
+      </c>
+      <c r="E16" s="17">
+        <v>4</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="H16" s="4">
+        <v>50</v>
+      </c>
+      <c r="I16" s="4">
+        <v>20</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9">
+        <f>MIN(1,AVERAGE(MIN(B16/500000,1),MIN(C16/60,1),D16/5,E16/5,IF(F16="да",1,0),IF(G16="да",1,0),MIN(H16/50,1),MIN(I16/6,1),IF(J16&gt;0,1,0)))</f>
+        <v>0.84444444444444444</v>
+      </c>
+      <c r="L16" s="18">
+        <f>IF(K16&gt;=0.7,5,IF(K16&gt;=0.4,3,1))</f>
+        <v>5</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="142.5">
       <c r="A17" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="B17" s="10">
+        <v>3000000</v>
+      </c>
+      <c r="C17" s="17">
+        <v>100</v>
+      </c>
+      <c r="D17" s="17">
+        <v>4</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="H17" s="4">
+        <v>10</v>
+      </c>
+      <c r="I17" s="4">
+        <v>3</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0</v>
+      </c>
+      <c r="K17" s="9">
+        <f>MIN(1,AVERAGE(MIN(B17/500000,1),MIN(C17/60,1),D17/5,E17/5,IF(F17="да",1,0),IF(G17="да",1,0),MIN(H17/50,1),MIN(I17/6,1),IF(J17&gt;0,1,0)))</f>
+        <v>0.67777777777777781</v>
+      </c>
+      <c r="L17" s="18">
+        <f>IF(K17&gt;=0.7,5,IF(K17&gt;=0.4,3,1))</f>
+        <v>3</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="171">
       <c r="A18" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="2"/>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="B18" s="10">
+        <v>476000000</v>
+      </c>
+      <c r="C18" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D18" s="17">
+        <v>5</v>
+      </c>
+      <c r="E18" s="17">
+        <v>5</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="H18" s="4">
+        <v>50</v>
+      </c>
+      <c r="I18" s="4">
+        <v>50</v>
+      </c>
+      <c r="J18" s="4">
+        <v>1</v>
+      </c>
+      <c r="K18" s="9">
+        <f>MIN(1,AVERAGE(MIN(B18/500000,1),MIN(C18/60,1),D18/5,E18/5,IF(F18="да",1,0),IF(G18="да",1,0),MIN(H18/50,1),MIN(I18/6,1),IF(J18&gt;0,1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="L18" s="18">
+        <f>IF(K18&gt;=0.7,5,IF(K18&gt;=0.4,3,1))</f>
+        <v>5</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="114">
       <c r="A19" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="2"/>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="B19" s="10">
+        <v>0</v>
+      </c>
+      <c r="C19" s="17">
+        <v>5</v>
+      </c>
+      <c r="D19" s="17">
+        <v>3</v>
+      </c>
+      <c r="E19" s="17">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4">
+        <v>1</v>
+      </c>
+      <c r="K19" s="9">
+        <f>MIN(1,AVERAGE(MIN(B19/500000,1),MIN(C19/60,1),D19/5,E19/5,IF(F19="да",1,0),IF(G19="да",1,0),MIN(H19/50,1),MIN(I19/6,1),IF(J19&gt;0,1,0)))</f>
+        <v>0.32037037037037036</v>
+      </c>
+      <c r="L19" s="18">
+        <f>IF(K19&gt;=0.7,5,IF(K19&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="128.25">
       <c r="A20" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="18"/>
-      <c r="M20" s="2"/>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="B20" s="10">
+        <v>0</v>
+      </c>
+      <c r="C20" s="17">
+        <v>30</v>
+      </c>
+      <c r="D20" s="17">
+        <v>3</v>
+      </c>
+      <c r="E20" s="17">
+        <v>2</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="H20" s="4">
+        <v>2</v>
+      </c>
+      <c r="I20" s="4">
+        <v>2</v>
+      </c>
+      <c r="J20" s="4">
+        <v>1</v>
+      </c>
+      <c r="K20" s="9">
+        <f>MIN(1,AVERAGE(MIN(B20/500000,1),MIN(C20/60,1),D20/5,E20/5,IF(F20="да",1,0),IF(G20="да",1,0),MIN(H20/50,1),MIN(I20/6,1),IF(J20&gt;0,1,0)))</f>
+        <v>0.4303703703703704</v>
+      </c>
+      <c r="L20" s="18">
+        <f>IF(K20&gt;=0.7,5,IF(K20&gt;=0.4,3,1))</f>
+        <v>3</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="85.5">
       <c r="A21" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="18"/>
-      <c r="M21" s="2"/>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="B21" s="10">
+        <v>0</v>
+      </c>
+      <c r="C21" s="17">
+        <v>5</v>
+      </c>
+      <c r="D21" s="17">
+        <v>2</v>
+      </c>
+      <c r="E21" s="17">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="H21" s="4">
+        <v>1</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4">
+        <v>0</v>
+      </c>
+      <c r="K21" s="9">
+        <f>MIN(1,AVERAGE(MIN(B21/500000,1),MIN(C21/60,1),D21/5,E21/5,IF(F21="да",1,0),IF(G21="да",1,0),MIN(H21/50,1),MIN(I21/6,1),IF(J21&gt;0,1,0)))</f>
+        <v>0.18925925925925927</v>
+      </c>
+      <c r="L21" s="18">
+        <f>IF(K21&gt;=0.7,5,IF(K21&gt;=0.4,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="128.25">
       <c r="A22" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="18"/>
-      <c r="M22" s="2"/>
+      <c r="B22" s="10">
+        <v>4000000</v>
+      </c>
+      <c r="C22" s="17">
+        <v>15</v>
+      </c>
+      <c r="D22" s="17">
+        <v>3</v>
+      </c>
+      <c r="E22" s="17">
+        <v>2</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="H22" s="4">
+        <v>5</v>
+      </c>
+      <c r="I22" s="4">
+        <v>3</v>
+      </c>
+      <c r="J22" s="4">
+        <v>1</v>
+      </c>
+      <c r="K22" s="9">
+        <f>MIN(1,AVERAGE(MIN(B22/500000,1),MIN(C22/60,1),D22/5,E22/5,IF(F22="да",1,0),IF(G22="да",1,0),MIN(H22/50,1),MIN(I22/6,1),IF(J22&gt;0,1,0)))</f>
+        <v>0.53888888888888886</v>
+      </c>
+      <c r="L22" s="18">
+        <f>IF(K22&gt;=0.7,5,IF(K22&gt;=0.4,3,1))</f>
+        <v>3</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="4"/>
@@ -7269,13 +8248,13 @@
       <c r="A37" t="s">
         <v>229</v>
       </c>
-      <c r="B37" s="13" t="e">
+      <c r="B37" s="13">
         <f>AVERAGE(K4:K33)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C37" t="e">
+        <v>0.35869395711500979</v>
+      </c>
+      <c r="C37" t="str">
         <f>IF(B37&gt;=0.7,"высокая",IF(B37&gt;=0.4,"средняя","низкая"))</f>
-        <v>#DIV/0!</v>
+        <v>низкая</v>
       </c>
       <c r="D37" t="s">
         <v>230</v>
@@ -7287,11 +8266,11 @@
       </c>
       <c r="B38" s="13">
         <f>SUMPRODUCT(--(((F4:F33="да")+(G4:G33="да"))&gt;0))/COUNTA(A4:A33)</f>
-        <v>0</v>
+        <v>0.52631578947368418</v>
       </c>
       <c r="C38" t="str">
         <f>IF(B38&gt;=0.75,"высокая цифровая зрелость",IF(B38&gt;=0.35,"средняя цифровая зрелость","низкая цифровая зрелость"))</f>
-        <v>низкая цифровая зрелость</v>
+        <v>средняя цифровая зрелость</v>
       </c>
       <c r="D38" t="s">
         <v>232</v>
@@ -7468,24 +8447,24 @@
       <c r="B6" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C6" s="9" t="e">
+      <c r="C6" s="9">
         <f>AVERAGE('03_Каналы_трафика'!C6,'04_Поиск_реклама'!B37)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D6" s="20" t="e">
+        <v>0.17543748305364212</v>
+      </c>
+      <c r="D6" s="20">
         <f>IF(C6&gt;=0.6,5,IF(C6&gt;=0.35,3,1))</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="E6" s="21">
         <v>0.12</v>
       </c>
-      <c r="F6" s="22" t="e">
+      <c r="F6" s="22">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G6" s="2" t="e">
+        <v>0.12</v>
+      </c>
+      <c r="G6" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>низкое</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>252</v>
@@ -7534,24 +8513,24 @@
       <c r="B8" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C8" s="9" t="e">
+      <c r="C8" s="9">
         <f>'04_Поиск_реклама'!B37</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D8" s="20" t="e">
+        <v>0.34339999999999998</v>
+      </c>
+      <c r="D8" s="20">
         <f>IF(C8&gt;=0.7,5,IF(C8&gt;=0.4,3,1))</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="E8" s="21">
         <v>0.12</v>
       </c>
-      <c r="F8" s="22" t="e">
+      <c r="F8" s="22">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G8" s="2" t="e">
+        <v>0.12</v>
+      </c>
+      <c r="G8" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>низкое</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>260</v>
@@ -7567,24 +8546,24 @@
       <c r="B9" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C9" s="9" t="e">
+      <c r="C9" s="9">
         <f>'05_Отзывы_рейтинги'!B37</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D9" s="20" t="e">
+        <v>0.35675438596491238</v>
+      </c>
+      <c r="D9" s="20">
         <f>IF(C9&gt;=0.7,5,IF(C9&gt;=0.4,3,1))</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="E9" s="21">
         <v>0.12</v>
       </c>
-      <c r="F9" s="22" t="e">
+      <c r="F9" s="22">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G9" s="2" t="e">
+        <v>0.12</v>
+      </c>
+      <c r="G9" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>низкое</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>264</v>
@@ -7600,24 +8579,24 @@
       <c r="B10" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C10" s="9" t="e">
+      <c r="C10" s="9">
         <f>'06_Технологии_финансы'!B37</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D10" s="20" t="e">
+        <v>0.35869395711500979</v>
+      </c>
+      <c r="D10" s="20">
         <f>IF(C10&gt;=0.7,5,IF(C10&gt;=0.4,3,1))</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="E10" s="21">
         <v>0.12</v>
       </c>
-      <c r="F10" s="22" t="e">
+      <c r="F10" s="22">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G10" s="2" t="e">
+        <v>0.12</v>
+      </c>
+      <c r="G10" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>низкое</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>268</v>
@@ -7695,25 +8674,25 @@
         <v>278</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="8" t="e">
+      <c r="C13" s="8">
         <f>SUM(F4:F12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D13" s="22" t="e">
+        <v>2.3200000000000003</v>
+      </c>
+      <c r="D13" s="22">
         <f>C13</f>
-        <v>#DIV/0!</v>
+        <v>2.3200000000000003</v>
       </c>
       <c r="E13" s="21">
         <f>SUM(E4:E12)</f>
         <v>1.04</v>
       </c>
-      <c r="F13" s="22" t="e">
+      <c r="F13" s="22">
         <f>SUM(F4:F12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G13" s="2" t="e">
+        <v>2.3200000000000003</v>
+      </c>
+      <c r="G13" s="2" t="str">
         <f>IF(F13&gt;=4,"высокие барьеры",IF(F13&gt;=2.5,"средние барьеры","низкие барьеры"))</f>
-        <v>#DIV/0!</v>
+        <v>низкие барьеры</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>279</v>
@@ -7805,7 +8784,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="33.950000000000003" customHeight="1">
@@ -7838,16 +8817,16 @@
       <c r="A5" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B5" s="22" t="e">
+      <c r="B5" s="22">
         <f>'07_Барьеры_входа'!F13</f>
-        <v>#DIV/0!</v>
+        <v>2.3200000000000003</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D5" s="2" t="e">
+      <c r="D5" s="2" t="str">
         <f>IF(B5&gt;=4,"Рынок труден для входа: нужны ресурсы, нишевание или сильное отличие.",IF(B5&gt;=2.5,"Вход возможен, но требует проверки каналов и позиционирования.","Барьеры относительно низкие, но требуется проверка платежеспособности."))</f>
-        <v>#DIV/0!</v>
+        <v>Барьеры относительно низкие, но требуется проверка платежеспособности.</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>242</v>
@@ -7869,9 +8848,9 @@
       <c r="A6" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="B6" s="2" t="e">
+      <c r="B6" s="2" t="str">
         <f>'07_Барьеры_входа'!G13</f>
-        <v>#DIV/0!</v>
+        <v>низкие барьеры</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -7909,17 +8888,17 @@
       <c r="F7" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="G7" s="22" t="e">
+      <c r="G7" s="22">
         <f>'07_Барьеры_входа'!D6</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="H7" s="22">
         <f>'07_Барьеры_входа'!E6</f>
         <v>0.12</v>
       </c>
-      <c r="I7" s="22" t="e">
+      <c r="I7" s="22">
         <f>'07_Барьеры_входа'!F6</f>
-        <v>#DIV/0!</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -7954,9 +8933,9 @@
       <c r="A9" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B9" s="8" t="e">
+      <c r="B9" s="8">
         <f>'04_Поиск_реклама'!B37</f>
-        <v>#DIV/0!</v>
+        <v>0.34339999999999998</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>80</v>
@@ -7965,26 +8944,26 @@
       <c r="F9" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="G9" s="22" t="e">
+      <c r="G9" s="22">
         <f>'07_Барьеры_входа'!D8</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="H9" s="22">
         <f>'07_Барьеры_входа'!E8</f>
         <v>0.12</v>
       </c>
-      <c r="I9" s="22" t="e">
+      <c r="I9" s="22">
         <f>'07_Барьеры_входа'!F8</f>
-        <v>#DIV/0!</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="28.5">
       <c r="A10" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B10" s="8" t="e">
+      <c r="B10" s="8">
         <f>'05_Отзывы_рейтинги'!B37</f>
-        <v>#DIV/0!</v>
+        <v>0.35675438596491238</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>80</v>
@@ -7993,26 +8972,26 @@
       <c r="F10" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="G10" s="22" t="e">
+      <c r="G10" s="22">
         <f>'07_Барьеры_входа'!D9</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="H10" s="22">
         <f>'07_Барьеры_входа'!E9</f>
         <v>0.12</v>
       </c>
-      <c r="I10" s="22" t="e">
+      <c r="I10" s="22">
         <f>'07_Барьеры_входа'!F9</f>
-        <v>#DIV/0!</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B11" s="8" t="e">
+      <c r="B11" s="8">
         <f>'06_Технологии_финансы'!B37</f>
-        <v>#DIV/0!</v>
+        <v>0.35869395711500979</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>80</v>
@@ -8021,17 +9000,17 @@
       <c r="F11" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="G11" s="22" t="e">
+      <c r="G11" s="22">
         <f>'07_Барьеры_входа'!D10</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="H11" s="22">
         <f>'07_Барьеры_входа'!E10</f>
         <v>0.12</v>
       </c>
-      <c r="I11" s="22" t="e">
+      <c r="I11" s="22">
         <f>'07_Барьеры_входа'!F10</f>
-        <v>#DIV/0!</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -8078,7 +9057,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="29" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="B15" s="29"/>
       <c r="C15" s="29"/>
